--- a/role.xlsx
+++ b/role.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samio\Documents\BUT\BUT3\S5\SAE\TP\Etape8\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDDFC77-E837-4C4B-BD2A-3D6D8697EBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,85 +18,12 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
-  <si>
-    <t>Role Name</t>
-  </si>
-  <si>
-    <t>ldap-admin-role</t>
-  </si>
-  <si>
-    <t>Accès complet LDAP</t>
-  </si>
-  <si>
-    <t>alice</t>
-  </si>
-  <si>
-    <t>LDAP RH</t>
-  </si>
-  <si>
-    <t>Super Use</t>
-  </si>
-  <si>
-    <t>Super User</t>
-  </si>
-  <si>
-    <t>Read Only</t>
-  </si>
-  <si>
-    <t>bob@gmeil.com</t>
-  </si>
-  <si>
-    <t>bob</t>
-  </si>
-  <si>
-    <t>alice@gmail.com</t>
-  </si>
-  <si>
-    <t>charlie@gmail.com</t>
-  </si>
-  <si>
-    <t>charlie</t>
-  </si>
-  <si>
-    <t>david</t>
-  </si>
-  <si>
-    <t>david@gmail.com</t>
-  </si>
-  <si>
-    <t>Role Description</t>
-  </si>
-  <si>
-    <t>User Name</t>
-  </si>
-  <si>
-    <t>User Emai</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
-    <t>Permission</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,16 +46,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -412,117 +330,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{FEE3F53E-5421-4E65-A9CB-8AB92CA99253}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{BD62A86F-E6C0-4F60-82DC-0297BE8CDE0B}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{6BADD935-9E07-4950-B8AB-E880202CED2D}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{27DD6D61-0747-4631-868A-44F910D9888D}"/>
-  </hyperlinks>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>